--- a/docs/collections/komabalib_rarematerial/metadata/data.xlsx
+++ b/docs/collections/komabalib_rarematerial/metadata/data.xlsx
@@ -413,106 +413,151 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T2"/>
+  <dimension ref="A1:AC29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>タイトル</t>
+          <t>タイトル/Title</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>書誌情報/Bibliographic Information</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>請求記号/Call No.</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>タイトル（ヨミ）</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>資料番号/Barcode No.</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>所蔵図書館室/Holding Library</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>書誌ID</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>巻</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>メモ</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>文庫区分</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t>iiif viewer</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>ウェブサイトURL</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>アイテムURL</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>利用条件</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>サムネイル</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>機械可読ドキュメント</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>帰属</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>viewingDirection</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>viewingHint</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>コレクション</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>ソート用項目</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>西暦</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>IIIFマニフェストURI</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>IIIF Search API URI</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>アノテーション付きIIIFマニフェストURI</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Link to TAPAS Project</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Text with Rich Text Format</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t># of media</t>
         </is>
@@ -526,96 +571,3300 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>dcterms:description</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>dcndl:callNumber</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>dcndl:titleTranscription</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>dcterms:identifier</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>dcndl:holdingAgent</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>dcndl:sourceIdentifier</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>dcndl:volume</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>archiveshub:note</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>uterms:bunko</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>iiif viewer</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>bibo:identifier</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>dcterms:isPartOf</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>dcterms:relation</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>dcterms:rights</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>foaf:thumbnail</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>rdfs:seeAlso</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>sc:attributionLabel</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>sc:viewingDirection</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>sc:viewingHint</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>uterms:databaseLabel</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>uterms:sort</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>uterms:year</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>uterms:manifestUri</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>uterms:searchApiUri</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>uterms:annotedManifest</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>uterms:linkToTapas</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>uterms:rtf</t>
         </is>
       </c>
-      <c r="T2" t="n">
-        <v>0</v>
+      <c r="AC2" t="n">
+        <v>1393</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>尾張名所圖會 [1]</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>尾張名所圖會 / 岡田啓(文園), 野口道直(梅居)仝撰 ; 小田切忠近(春江)圖畫 ; 前編巻之1 - 後編巻之6. -- 片野東四郎, 1880. -- 13冊 : 挿図 ; 26cm.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>090:2:21-1</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>オワリ メイショ ズエ</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>3003193228</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>駒場図書館</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2000744089</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>前編巻之1</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>江戸古版本</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/d36c2c60-9f38-415e-931a-8a0994803862.json</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>d36c2c60-9f38-415e-931a-8a0994803862</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/komabalib_rarematerial</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/komabalib_rarematerial/document/d36c2c60-9f38-415e-931a-8a0994803862</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>https://www.lib.u-tokyo.ac.jp/ja/library/komaba/user-guide/special-use/archives-data</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/54de4539ea9dd6ad41e9e7693f111704b7bd9a37.jpg</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1228295</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>東京大学駒場図書館 Komaba Library, The University of Tokyo, JAPAN</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>駒場図書館貴重資料デジタルコレクション</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>edokohan-001</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/d36c2c60-9f38-415e-931a-8a0994803862/manifest</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="n">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>尾張名所圖會 [2]</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>尾張名所圖會 / 岡田啓(文園), 野口道直(梅居)仝撰 ; 小田切忠近(春江)圖畫 ; 前編巻之1 - 後編巻之6. -- 片野東四郎, 1880. -- 13冊 : 挿図 ; 26cm.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>090:2:21-1</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>オワリ メイショ ズエ</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>3003193236</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>駒場図書館</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2000744089</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>前編巻之2</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>江戸古版本</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/66405104-9002-19bd-7921-6af895c63863.json</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>66405104-9002-19bd-7921-6af895c63863</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/komabalib_rarematerial</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/komabalib_rarematerial/document/66405104-9002-19bd-7921-6af895c63863</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>https://www.lib.u-tokyo.ac.jp/ja/library/komaba/user-guide/special-use/archives-data</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/c31d47f826a46060d333a183dfff21686339b7e1.jpg</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1228296</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>東京大学駒場図書館 Komaba Library, The University of Tokyo, JAPAN</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>駒場図書館貴重資料デジタルコレクション</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>edokohan-002</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/66405104-9002-19bd-7921-6af895c63863/manifest</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>尾張名所圖會 [3]</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>尾張名所圖會 / 岡田啓(文園), 野口道直(梅居)仝撰 ; 小田切忠近(春江)圖畫 ; 前編巻之1 - 後編巻之6. -- 片野東四郎, 1880. -- 13冊 : 挿図 ; 26cm.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>090:2:21-1</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>オワリ メイショ ズエ</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>3003193244</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>駒場図書館</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2000744089</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>前編巻之3</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>江戸古版本</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/0988d84d-3649-015c-881a-cd78373f52e7.json</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>0988d84d-3649-015c-881a-cd78373f52e7</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/komabalib_rarematerial</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/komabalib_rarematerial/document/0988d84d-3649-015c-881a-cd78373f52e7</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>https://www.lib.u-tokyo.ac.jp/ja/library/komaba/user-guide/special-use/archives-data</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/b4889062171e491f3d501d4bfda9f171b35ebfbe.jpg</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1228297</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>東京大学駒場図書館 Komaba Library, The University of Tokyo, JAPAN</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>駒場図書館貴重資料デジタルコレクション</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>edokohan-003</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/0988d84d-3649-015c-881a-cd78373f52e7/manifest</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>尾張名所圖會 [4]</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>尾張名所圖會 / 岡田啓(文園), 野口道直(梅居)仝撰 ; 小田切忠近(春江)圖畫 ; 前編巻之1 - 後編巻之6. -- 片野東四郎, 1880. -- 13冊 : 挿図 ; 26cm.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>090:2:21-1</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>オワリ メイショ ズエ</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>3003193251</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>駒場図書館</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2000744089</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>前編巻之4</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>江戸古版本</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/4b543247-2192-105b-8bad-e70ce6568ec7.json</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>4b543247-2192-105b-8bad-e70ce6568ec7</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/komabalib_rarematerial</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/komabalib_rarematerial/document/4b543247-2192-105b-8bad-e70ce6568ec7</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>https://www.lib.u-tokyo.ac.jp/ja/library/komaba/user-guide/special-use/archives-data</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/c441f3136fc167e84ad665ee0b6e050256b66ba3.jpg</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1228298</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>東京大学駒場図書館 Komaba Library, The University of Tokyo, JAPAN</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>駒場図書館貴重資料デジタルコレクション</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>edokohan-004</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/4b543247-2192-105b-8bad-e70ce6568ec7/manifest</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>尾張名所圖會 [5]</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>尾張名所圖會 / 岡田啓(文園), 野口道直(梅居)仝撰 ; 小田切忠近(春江)圖畫 ; 前編巻之1 - 後編巻之6. -- 片野東四郎, 1880. -- 13冊 : 挿図 ; 26cm.</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>090:2:21-1</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>オワリ メイショ ズエ</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>3003193269</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>駒場図書館</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2000744089</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>前編巻之5</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>江戸古版本</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/9d125b84-2424-1e38-2714-fcd3625b2a4b.json</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>9d125b84-2424-1e38-2714-fcd3625b2a4b</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/komabalib_rarematerial</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/komabalib_rarematerial/document/9d125b84-2424-1e38-2714-fcd3625b2a4b</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>https://www.lib.u-tokyo.ac.jp/ja/library/komaba/user-guide/special-use/archives-data</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/12db5afb7402ebc1190d06fba12cfdf76a7a47d3.jpg</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1228299</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>東京大学駒場図書館 Komaba Library, The University of Tokyo, JAPAN</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>駒場図書館貴重資料デジタルコレクション</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>edokohan-005</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/9d125b84-2424-1e38-2714-fcd3625b2a4b/manifest</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="n">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>尾張名所圖會 [6]</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>尾張名所圖會 / 岡田啓(文園), 野口道直(梅居)仝撰 ; 小田切忠近(春江)圖畫 ; 前編巻之1 - 後編巻之6. -- 片野東四郎, 1880. -- 13冊 : 挿図 ; 26cm.</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>090:2:21-1</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>オワリ メイショ ズエ</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>3003193277</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>駒場図書館</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2000744089</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>前編巻之6</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>江戸古版本</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/e825f8e3-28ac-a24d-9cf5-b2cf72e205f9.json</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>e825f8e3-28ac-a24d-9cf5-b2cf72e205f9</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/komabalib_rarematerial</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/komabalib_rarematerial/document/e825f8e3-28ac-a24d-9cf5-b2cf72e205f9</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>https://www.lib.u-tokyo.ac.jp/ja/library/komaba/user-guide/special-use/archives-data</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/3366f240d3677979696783eac2b98c2a22050371.jpg</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1228300</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>東京大学駒場図書館 Komaba Library, The University of Tokyo, JAPAN</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>駒場図書館貴重資料デジタルコレクション</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>edokohan-006</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/e825f8e3-28ac-a24d-9cf5-b2cf72e205f9/manifest</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>尾張名所圖會 [7]</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>尾張名所圖會 / 岡田啓(文園), 野口道直(梅居)仝撰 ; 小田切忠近(春江)圖畫 ; 前編巻之1 - 後編巻之6. -- 片野東四郎, 1880. -- 13冊 : 挿図 ; 26cm.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>090:2:21-1</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>オワリ メイショ ズエ</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>3003193285</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>駒場図書館</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2000744089</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>前編巻之7</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>江戸古版本</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/cab63b57-714a-4518-0f3f-3a092aeb1a8e.json</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>cab63b57-714a-4518-0f3f-3a092aeb1a8e</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/komabalib_rarematerial</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/komabalib_rarematerial/document/cab63b57-714a-4518-0f3f-3a092aeb1a8e</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>https://www.lib.u-tokyo.ac.jp/ja/library/komaba/user-guide/special-use/archives-data</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/ec104afe93bee10c1d8b4ed6935c103e219f73a4.jpg</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1228301</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>東京大学駒場図書館 Komaba Library, The University of Tokyo, JAPAN</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>駒場図書館貴重資料デジタルコレクション</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>edokohan-007</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/cab63b57-714a-4518-0f3f-3a092aeb1a8e/manifest</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="n">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>尾張名所圖會 [8]</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>尾張名所圖會 / 岡田啓(文園), 野口道直(梅居)仝撰 ; 小田切忠近(春江)圖畫 ; 前編巻之1 - 後編巻之6. -- 片野東四郎, 1880. -- 13冊 : 挿図 ; 26cm.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>090:2:21-2</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>オワリ メイショ ズエ</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>3003193293</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>駒場図書館</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2000744089</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>後編巻之1</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>江戸古版本</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/c888ffea-0910-1b01-3454-e9a2df511aa9.json</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>c888ffea-0910-1b01-3454-e9a2df511aa9</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/komabalib_rarematerial</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/komabalib_rarematerial/document/c888ffea-0910-1b01-3454-e9a2df511aa9</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>https://www.lib.u-tokyo.ac.jp/ja/library/komaba/user-guide/special-use/archives-data</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/44b3c63a88ce49871fe1da153adf9bf9aa4809fc.jpg</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1228302</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>東京大学駒場図書館 Komaba Library, The University of Tokyo, JAPAN</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>駒場図書館貴重資料デジタルコレクション</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>edokohan-008</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/c888ffea-0910-1b01-3454-e9a2df511aa9/manifest</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>尾張名所圖會 [9]</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>尾張名所圖會 / 岡田啓(文園), 野口道直(梅居)仝撰 ; 小田切忠近(春江)圖畫 ; 前編巻之1 - 後編巻之6. -- 片野東四郎, 1880. -- 13冊 : 挿図 ; 26cm.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>090:2:21-2</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>オワリ メイショ ズエ</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>3003193301</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>駒場図書館</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2000744089</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>後編巻之2</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>江戸古版本</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/6ab117bb-19da-405b-a420-e521b2398fd2.json</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>6ab117bb-19da-405b-a420-e521b2398fd2</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/komabalib_rarematerial</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/komabalib_rarematerial/document/6ab117bb-19da-405b-a420-e521b2398fd2</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>https://www.lib.u-tokyo.ac.jp/ja/library/komaba/user-guide/special-use/archives-data</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/bf3f25cf705d9ee7cf6ad192c4db59efa132c7ff.jpg</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1228303</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>東京大学駒場図書館 Komaba Library, The University of Tokyo, JAPAN</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>駒場図書館貴重資料デジタルコレクション</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>edokohan-009</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/6ab117bb-19da-405b-a420-e521b2398fd2/manifest</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>尾張名所圖會 [10]</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>尾張名所圖會 / 岡田啓(文園), 野口道直(梅居)仝撰 ; 小田切忠近(春江)圖畫 ; 前編巻之1 - 後編巻之6. -- 片野東四郎, 1880. -- 13冊 : 挿図 ; 26cm.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>090:2:21-2</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>オワリ メイショ ズエ</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>3003193319</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>駒場図書館</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2000744089</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>後編巻之3</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>江戸古版本</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/3abe91bb-8b34-730a-8620-97570b598be7.json</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>3abe91bb-8b34-730a-8620-97570b598be7</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/komabalib_rarematerial</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/komabalib_rarematerial/document/3abe91bb-8b34-730a-8620-97570b598be7</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>https://www.lib.u-tokyo.ac.jp/ja/library/komaba/user-guide/special-use/archives-data</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/cd09ca15951b9caf791f9b6daf34705ddaccd2a3.jpg</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1228304</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>東京大学駒場図書館 Komaba Library, The University of Tokyo, JAPAN</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>駒場図書館貴重資料デジタルコレクション</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>edokohan-010</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/3abe91bb-8b34-730a-8620-97570b598be7/manifest</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>尾張名所圖會 [11]</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>尾張名所圖會 / 岡田啓(文園), 野口道直(梅居)仝撰 ; 小田切忠近(春江)圖畫 ; 前編巻之1 - 後編巻之6. -- 片野東四郎, 1880. -- 13冊 : 挿図 ; 26cm.</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>090:2:21-2</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>オワリ メイショ ズエ</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>3003193327</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>駒場図書館</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2000744089</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>後編巻之4</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>江戸古版本</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/e90e3671-760b-502c-4567-f7dc6a96259b.json</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>e90e3671-760b-502c-4567-f7dc6a96259b</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/komabalib_rarematerial</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/komabalib_rarematerial/document/e90e3671-760b-502c-4567-f7dc6a96259b</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>https://www.lib.u-tokyo.ac.jp/ja/library/komaba/user-guide/special-use/archives-data</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/c617b6ea053c96c4f71dfa3665a6a6c4067efe03.jpg</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1228305</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>東京大学駒場図書館 Komaba Library, The University of Tokyo, JAPAN</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>駒場図書館貴重資料デジタルコレクション</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>edokohan-011</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/e90e3671-760b-502c-4567-f7dc6a96259b/manifest</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>尾張名所圖會 [12]</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>尾張名所圖會 / 岡田啓(文園), 野口道直(梅居)仝撰 ; 小田切忠近(春江)圖畫 ; 前編巻之1 - 後編巻之6. -- 片野東四郎, 1880. -- 13冊 : 挿図 ; 26cm.</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>090:2:21-2</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>オワリ メイショ ズエ</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>3003193335</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>駒場図書館</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2000744089</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>後編巻之5</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>江戸古版本</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/acd7b9d4-2c09-56e8-53af-259255ce7824.json</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>acd7b9d4-2c09-56e8-53af-259255ce7824</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/komabalib_rarematerial</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/komabalib_rarematerial/document/acd7b9d4-2c09-56e8-53af-259255ce7824</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>https://www.lib.u-tokyo.ac.jp/ja/library/komaba/user-guide/special-use/archives-data</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/f6b477e67cc885971682f12353445caabca362a7.jpg</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1228306</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>東京大学駒場図書館 Komaba Library, The University of Tokyo, JAPAN</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>駒場図書館貴重資料デジタルコレクション</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>edokohan-012</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/acd7b9d4-2c09-56e8-53af-259255ce7824/manifest</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>尾張名所圖會 [13]</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>尾張名所圖會 / 岡田啓(文園), 野口道直(梅居)仝撰 ; 小田切忠近(春江)圖畫 ; 前編巻之1 - 後編巻之6. -- 片野東四郎, 1880. -- 13冊 : 挿図 ; 26cm.</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>090:2:21-2</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>オワリ メイショ ズエ</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>3003193343</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>駒場図書館</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2000744089</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>後編巻之6</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>江戸古版本</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/82727f77-757a-1778-0451-c133cd839b29.json</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>82727f77-757a-1778-0451-c133cd839b29</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/komabalib_rarematerial</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/komabalib_rarematerial/document/82727f77-757a-1778-0451-c133cd839b29</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>https://www.lib.u-tokyo.ac.jp/ja/library/komaba/user-guide/special-use/archives-data</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/46c8b2de82a78560301c731128996a218a8f2833.jpg</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1228307</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>東京大学駒場図書館 Komaba Library, The University of Tokyo, JAPAN</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>駒場図書館貴重資料デジタルコレクション</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>edokohan-013</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/82727f77-757a-1778-0451-c133cd839b29/manifest</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="n">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>下野國誌 12巻 [1]</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>下野國誌 12巻 / 越智守弘識 ; 1之卷 - 12之卷. -- 須原屋茂兵衛, [明治期] [印]. -- 12冊 : 挿図 ; 26cm.</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>090:2:22</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>シモツケ コクシ</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>3003193350</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>駒場図書館</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2003292309</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>1之卷</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>江戸古版本</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/42f660c1-29f0-105b-62ec-75d8aae41cd3.json</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>42f660c1-29f0-105b-62ec-75d8aae41cd3</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/komabalib_rarematerial</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/komabalib_rarematerial/document/42f660c1-29f0-105b-62ec-75d8aae41cd3</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>https://www.lib.u-tokyo.ac.jp/ja/library/komaba/user-guide/special-use/archives-data</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/9666488d3d01c9d1dbc5d2d12e677c71c451b1fe.jpg</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1228308</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>東京大学駒場図書館 Komaba Library, The University of Tokyo, JAPAN</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>駒場図書館貴重資料デジタルコレクション</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>edokohan-014</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/42f660c1-29f0-105b-62ec-75d8aae41cd3/manifest</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>下野國誌 12巻 [2]</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>下野國誌 12巻 / 越智守弘識 ; 1之卷 - 12之卷. -- 須原屋茂兵衛, [明治期] [印]. -- 12冊 : 挿図 ; 26cm.</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>090:2:22</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>シモツケ コクシ</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>3003193368</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>駒場図書館</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>2003292309</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>2之卷</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>江戸古版本</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/3b7deb82-4551-7bee-4c05-632e5a460e67.json</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>3b7deb82-4551-7bee-4c05-632e5a460e67</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/komabalib_rarematerial</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/komabalib_rarematerial/document/3b7deb82-4551-7bee-4c05-632e5a460e67</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>https://www.lib.u-tokyo.ac.jp/ja/library/komaba/user-guide/special-use/archives-data</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/5edf0491f491e4bed0e607e794215cc568b8655c.jpg</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1228309</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>東京大学駒場図書館 Komaba Library, The University of Tokyo, JAPAN</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>駒場図書館貴重資料デジタルコレクション</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>edokohan-015</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/3b7deb82-4551-7bee-4c05-632e5a460e67/manifest</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr"/>
+      <c r="AC17" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>下野國誌 12巻 [3]</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>下野國誌 12巻 / 越智守弘識 ; 1之卷 - 12之卷. -- 須原屋茂兵衛, [明治期] [印]. -- 12冊 : 挿図 ; 26cm.</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>090:2:22</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>シモツケ コクシ</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>3003193376</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>駒場図書館</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2003292309</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>3之卷</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>江戸古版本</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/ae3e6ca0-a004-7a9c-36a9-4c26290e6be0.json</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>ae3e6ca0-a004-7a9c-36a9-4c26290e6be0</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/komabalib_rarematerial</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/komabalib_rarematerial/document/ae3e6ca0-a004-7a9c-36a9-4c26290e6be0</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>https://www.lib.u-tokyo.ac.jp/ja/library/komaba/user-guide/special-use/archives-data</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/ac639d8c272fea5019f3ac02210677fa5f292a4f.jpg</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1228310</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>東京大学駒場図書館 Komaba Library, The University of Tokyo, JAPAN</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>駒場図書館貴重資料デジタルコレクション</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>edokohan-016</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/ae3e6ca0-a004-7a9c-36a9-4c26290e6be0/manifest</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr"/>
+      <c r="AC18" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>下野國誌 12巻 [4]</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>下野國誌 12巻 / 越智守弘識 ; 1之卷 - 12之卷. -- 須原屋茂兵衛, [明治期] [印]. -- 12冊 : 挿図 ; 26cm.</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>090:2:22</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>シモツケ コクシ</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>3003193384</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>駒場図書館</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>2003292309</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>4之卷</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>江戸古版本</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/f088d0dd-57ce-35ca-8dc0-6bac2e5c9bb8.json</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>f088d0dd-57ce-35ca-8dc0-6bac2e5c9bb8</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/komabalib_rarematerial</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/komabalib_rarematerial/document/f088d0dd-57ce-35ca-8dc0-6bac2e5c9bb8</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>https://www.lib.u-tokyo.ac.jp/ja/library/komaba/user-guide/special-use/archives-data</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/ad04386779576a61b1d770356ce194644dc4d988.jpg</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1228311</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>東京大学駒場図書館 Komaba Library, The University of Tokyo, JAPAN</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>駒場図書館貴重資料デジタルコレクション</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>edokohan-017</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/f088d0dd-57ce-35ca-8dc0-6bac2e5c9bb8/manifest</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr"/>
+      <c r="AB19" t="inlineStr"/>
+      <c r="AC19" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>下野國誌 12巻 [5]</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>下野國誌 12巻 / 越智守弘識 ; 1之卷 - 12之卷. -- 須原屋茂兵衛, [明治期] [印]. -- 12冊 : 挿図 ; 26cm.</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>090:2:22</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>シモツケ コクシ</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>3003193392</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>駒場図書館</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2003292309</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>5之卷</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>江戸古版本</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/f8cece9b-8548-4811-7750-8b6ab0ce03d1.json</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>f8cece9b-8548-4811-7750-8b6ab0ce03d1</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/komabalib_rarematerial</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/komabalib_rarematerial/document/f8cece9b-8548-4811-7750-8b6ab0ce03d1</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>https://www.lib.u-tokyo.ac.jp/ja/library/komaba/user-guide/special-use/archives-data</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/2b421d2d2e6fd4cba9ce074a81368a3826632421.jpg</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1228312</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>東京大学駒場図書館 Komaba Library, The University of Tokyo, JAPAN</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>駒場図書館貴重資料デジタルコレクション</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>edokohan-018</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/f8cece9b-8548-4811-7750-8b6ab0ce03d1/manifest</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
+      <c r="AA20" t="inlineStr"/>
+      <c r="AB20" t="inlineStr"/>
+      <c r="AC20" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>下野國誌 12巻 [6]</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>下野國誌 12巻 / 越智守弘識 ; 1之卷 - 12之卷. -- 須原屋茂兵衛, [明治期] [印]. -- 12冊 : 挿図 ; 26cm.</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>090:2:22</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>シモツケ コクシ</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>3003193400</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>駒場図書館</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>2003292309</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>6之卷</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>江戸古版本</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/1693bef9-329d-16fb-711d-a654d6667707.json</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>1693bef9-329d-16fb-711d-a654d6667707</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/komabalib_rarematerial</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/komabalib_rarematerial/document/1693bef9-329d-16fb-711d-a654d6667707</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>https://www.lib.u-tokyo.ac.jp/ja/library/komaba/user-guide/special-use/archives-data</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/702638af086752f145a821c77d9988dc339f5f5e.jpg</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1228313</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>東京大学駒場図書館 Komaba Library, The University of Tokyo, JAPAN</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>駒場図書館貴重資料デジタルコレクション</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>edokohan-019</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr"/>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/1693bef9-329d-16fb-711d-a654d6667707/manifest</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr"/>
+      <c r="AA21" t="inlineStr"/>
+      <c r="AB21" t="inlineStr"/>
+      <c r="AC21" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>下野國誌 12巻 [7]</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>下野國誌 12巻 / 越智守弘識 ; 1之卷 - 12之卷. -- 須原屋茂兵衛, [明治期] [印]. -- 12冊 : 挿図 ; 26cm.</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>090:2:22</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>シモツケ コクシ</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>3003193418</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>駒場図書館</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>2003292309</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>7之卷</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>江戸古版本</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/4eb26c1c-8e9b-74e0-9f8a-f44fa4c414a4.json</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>4eb26c1c-8e9b-74e0-9f8a-f44fa4c414a4</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/komabalib_rarematerial</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/komabalib_rarematerial/document/4eb26c1c-8e9b-74e0-9f8a-f44fa4c414a4</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>https://www.lib.u-tokyo.ac.jp/ja/library/komaba/user-guide/special-use/archives-data</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/6d3774bcc8e0757f1d3db1b669e76619eb9ae3bc.jpg</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1228314</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>東京大学駒場図書館 Komaba Library, The University of Tokyo, JAPAN</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>駒場図書館貴重資料デジタルコレクション</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>edokohan-020</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr"/>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/4eb26c1c-8e9b-74e0-9f8a-f44fa4c414a4/manifest</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr"/>
+      <c r="AB22" t="inlineStr"/>
+      <c r="AC22" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>下野國誌 12巻 [8]</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>下野國誌 12巻 / 越智守弘識 ; 1之卷 - 12之卷. -- 須原屋茂兵衛, [明治期] [印]. -- 12冊 : 挿図 ; 26cm.</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>090:2:22</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>シモツケ コクシ</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>3003193426</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>駒場図書館</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2003292309</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>8之卷</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>江戸古版本</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/f2b6c292-2a2c-1b84-7573-9e54f87f5087.json</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>f2b6c292-2a2c-1b84-7573-9e54f87f5087</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/komabalib_rarematerial</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/komabalib_rarematerial/document/f2b6c292-2a2c-1b84-7573-9e54f87f5087</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>https://www.lib.u-tokyo.ac.jp/ja/library/komaba/user-guide/special-use/archives-data</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/574ca16c33201361c0d79b6ad1bc966019923c33.jpg</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1228315</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>東京大学駒場図書館 Komaba Library, The University of Tokyo, JAPAN</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>駒場図書館貴重資料デジタルコレクション</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>edokohan-021</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr"/>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/f2b6c292-2a2c-1b84-7573-9e54f87f5087/manifest</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
+      <c r="AA23" t="inlineStr"/>
+      <c r="AB23" t="inlineStr"/>
+      <c r="AC23" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>下野國誌 12巻 [9]</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>下野國誌 12巻 / 越智守弘識 ; 1之卷 - 12之卷. -- 須原屋茂兵衛, [明治期] [印]. -- 12冊 : 挿図 ; 26cm.</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>090:2:22</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>シモツケ コクシ</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>3003193434</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>駒場図書館</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>2003292309</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>9之卷</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>江戸古版本</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/fd70bb31-0e00-4bfa-7b40-14895a417dee.json</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>fd70bb31-0e00-4bfa-7b40-14895a417dee</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/komabalib_rarematerial</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/komabalib_rarematerial/document/fd70bb31-0e00-4bfa-7b40-14895a417dee</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>https://www.lib.u-tokyo.ac.jp/ja/library/komaba/user-guide/special-use/archives-data</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/7bafb87df9265a09e8967a58b5c51f355f39ce48.jpg</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1228316</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>東京大学駒場図書館 Komaba Library, The University of Tokyo, JAPAN</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>駒場図書館貴重資料デジタルコレクション</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>edokohan-022</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/fd70bb31-0e00-4bfa-7b40-14895a417dee/manifest</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr"/>
+      <c r="AB24" t="inlineStr"/>
+      <c r="AC24" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>下野國誌 12巻 [10]</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>下野國誌 12巻 / 越智守弘識 ; 1之卷 - 12之卷. -- 須原屋茂兵衛, [明治期] [印]. -- 12冊 : 挿図 ; 26cm.</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>090:2:22</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>シモツケ コクシ</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>3003193442</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>駒場図書館</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>2003292309</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>10之卷</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>江戸古版本</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/9b393cb2-89d3-5485-8aa0-51080039592f.json</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>9b393cb2-89d3-5485-8aa0-51080039592f</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/komabalib_rarematerial</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/komabalib_rarematerial/document/9b393cb2-89d3-5485-8aa0-51080039592f</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>https://www.lib.u-tokyo.ac.jp/ja/library/komaba/user-guide/special-use/archives-data</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/17f49c1edd88369cec3834ced3879697282f697c.jpg</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1228317</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>東京大学駒場図書館 Komaba Library, The University of Tokyo, JAPAN</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>駒場図書館貴重資料デジタルコレクション</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>edokohan-023</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr"/>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/9b393cb2-89d3-5485-8aa0-51080039592f/manifest</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr"/>
+      <c r="AB25" t="inlineStr"/>
+      <c r="AC25" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>下野國誌 12巻 [11]</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>下野國誌 12巻 / 越智守弘識 ; 1之卷 - 12之卷. -- 須原屋茂兵衛, [明治期] [印]. -- 12冊 : 挿図 ; 26cm.</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>090:2:22</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>シモツケ コクシ</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>3003193459</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>駒場図書館</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2003292309</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>11之卷</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>江戸古版本</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/84852a89-5ca8-922a-9511-3182fcd0464e.json</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>84852a89-5ca8-922a-9511-3182fcd0464e</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/komabalib_rarematerial</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/komabalib_rarematerial/document/84852a89-5ca8-922a-9511-3182fcd0464e</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>https://www.lib.u-tokyo.ac.jp/ja/library/komaba/user-guide/special-use/archives-data</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/c7afcd0f2e14a063d5fd405d907ebfb66e65a319.jpg</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1228318</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>東京大学駒場図書館 Komaba Library, The University of Tokyo, JAPAN</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>駒場図書館貴重資料デジタルコレクション</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>edokohan-024</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr"/>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/84852a89-5ca8-922a-9511-3182fcd0464e/manifest</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr"/>
+      <c r="AB26" t="inlineStr"/>
+      <c r="AC26" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>下野國誌 12巻 [12]</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>下野國誌 12巻 / 越智守弘識 ; 1之卷 - 12之卷. -- 須原屋茂兵衛, [明治期] [印]. -- 12冊 : 挿図 ; 26cm.</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>090:2:22</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>シモツケ コクシ</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>3003193467</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>駒場図書館</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2003292309</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>12之卷</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>江戸古版本</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/9d323cd5-38e0-85dd-3a44-5c21875c141e.json</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>9d323cd5-38e0-85dd-3a44-5c21875c141e</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/komabalib_rarematerial</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/komabalib_rarematerial/document/9d323cd5-38e0-85dd-3a44-5c21875c141e</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>https://www.lib.u-tokyo.ac.jp/ja/library/komaba/user-guide/special-use/archives-data</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/3b4f35546e96984487c2ce7280b27795bed586f3.jpg</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1228319</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>東京大学駒場図書館 Komaba Library, The University of Tokyo, JAPAN</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>駒場図書館貴重資料デジタルコレクション</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>edokohan-025</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr"/>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/9d323cd5-38e0-85dd-3a44-5c21875c141e/manifest</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr"/>
+      <c r="AB27" t="inlineStr"/>
+      <c r="AC27" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>芦のそよぎ 2巻</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>芦のそよぎ 2巻 / 太田花兄編輯. -- [書写者不明], [明治19 (1886)]. -- 1冊 : 挿図 ; 28cm. d.</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>090:2:211</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>アシ ノ ソヨギ</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>3003196627</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>駒場図書館</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2003292511</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>前編巻之2</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>江戸古版本</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/641b689d-5a68-9b94-982a-39210f0716f2.json</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>641b689d-5a68-9b94-982a-39210f0716f2</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/komabalib_rarematerial</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/komabalib_rarematerial/document/641b689d-5a68-9b94-982a-39210f0716f2</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>https://www.lib.u-tokyo.ac.jp/ja/library/komaba/user-guide/special-use/archives-data</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/2d3e6d1d7d7f88d457d69d920e65d045525ac5f9.jpg</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1228320</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>東京大学駒場図書館 Komaba Library, The University of Tokyo, JAPAN</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>駒場図書館貴重資料デジタルコレクション</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>edokohan-026</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr"/>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/641b689d-5a68-9b94-982a-39210f0716f2/manifest</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr"/>
+      <c r="AB28" t="inlineStr"/>
+      <c r="AC28" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>凉しさや揚屋も茶屋も男女川</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>凉しさや揚屋も茶屋も男女川. -- [出版者不明], [享保頃]. -- 1舗 ; 96×90cm (折りたたみ23×17cm).</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>090:2:178</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>スズシサヤ アゲヤ モ チャヤ モ ミナノガワ</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>3003196254</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>駒場図書館</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2003292478</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>前編巻之1</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>江戸古版本</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/b68e8657-5849-a1ba-3e16-f13055b34fd3.json</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>b68e8657-5849-a1ba-3e16-f13055b34fd3</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/komabalib_rarematerial</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/komabalib_rarematerial/document/b68e8657-5849-a1ba-3e16-f13055b34fd3</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>https://www.lib.u-tokyo.ac.jp/ja/library/komaba/user-guide/special-use/archives-data</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/8235824057b0324040b076aae0081c6472bbafcb.jpg</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1228321</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>東京大学駒場図書館 Komaba Library, The University of Tokyo, JAPAN</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>駒場図書館貴重資料デジタルコレクション</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>edokohan-027</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/b68e8657-5849-a1ba-3e16-f13055b34fd3/manifest</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr"/>
+      <c r="AB29" t="inlineStr"/>
+      <c r="AC29" t="n">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
